--- a/backend/news.xlsx
+++ b/backend/news.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,9 +433,26 @@
         <v>newsEvents/news/1777216296080_EUROPE_DESTINATIONS.png</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>N103</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Members Meet in KUSUMU/Kenya</v>
+      </c>
+      <c r="C3" t="str">
+        <v>09/22/2026</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Manish Mehta Got a wonderful opportunity to spend a meaningful evening over dinner cherishing his LE college time with Jayesh BHADANIA, 92 Civil⁩ (on the left)  and his family in Kisumu/kenya.</v>
+      </c>
+      <c r="E3" t="str">
+        <v>newsEvents/news/1790227482453_Kisumu_Kenya.jpeg</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>